--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_INSOLAC CAJA 87.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_INSOLAC CAJA 87.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>S. CECILIA PEREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>53.9453</v>
+        <v>49.5291</v>
       </c>
       <c r="E2" t="n">
-        <v>43.9916</v>
+        <v>37.1932</v>
       </c>
       <c r="F2" t="n">
-        <v>9.953200000000001</v>
+        <v>12.336</v>
       </c>
       <c r="G2" t="n">
-        <v>12.3898</v>
+        <v>8.652299999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>12.9619</v>
+        <v>-11.7758</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5723999999999998</v>
+        <v>20.4287</v>
       </c>
       <c r="J2" t="n">
-        <v>38.8268</v>
+        <v>32.7345</v>
       </c>
       <c r="K2" t="n">
-        <v>31.0758</v>
+        <v>7.0813</v>
       </c>
       <c r="L2" t="n">
-        <v>7.7508</v>
+        <v>25.6532</v>
       </c>
       <c r="M2" t="n">
-        <v>-26.4371</v>
+        <v>-24.0822</v>
       </c>
       <c r="N2" t="n">
-        <v>-18.114</v>
+        <v>-18.8573</v>
       </c>
       <c r="O2" t="n">
-        <v>-8.323</v>
+        <v>-5.2248</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6244000000000005</v>
+        <v>20.812</v>
       </c>
       <c r="Q2" t="n">
-        <v>-46.2025</v>
+        <v>-23.5175</v>
       </c>
       <c r="R2" t="n">
-        <v>45.5779</v>
+        <v>44.3292</v>
       </c>
       <c r="S2" t="n">
-        <v>33.5049</v>
+        <v>2.0284</v>
       </c>
       <c r="T2" t="n">
-        <v>25.2922</v>
+        <v>2.0785</v>
       </c>
       <c r="U2" t="n">
-        <v>8.2126</v>
+        <v>-0.04989999999999994</v>
       </c>
       <c r="V2" t="n">
-        <v>8.6752</v>
+        <v>18.0367</v>
       </c>
       <c r="W2" t="n">
-        <v>26.0749</v>
+        <v>25.8979</v>
       </c>
       <c r="X2" t="n">
-        <v>-17.3996</v>
+        <v>-7.8613</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. CECILIA PEREZ</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>38.0607</v>
+        <v>40.9864</v>
       </c>
       <c r="E3" t="n">
-        <v>30.4282</v>
+        <v>31.7062</v>
       </c>
       <c r="F3" t="n">
-        <v>7.632400000000001</v>
+        <v>9.2803</v>
       </c>
       <c r="G3" t="n">
-        <v>8.652299999999999</v>
+        <v>12.3898</v>
       </c>
       <c r="H3" t="n">
-        <v>-11.7758</v>
+        <v>12.9619</v>
       </c>
       <c r="I3" t="n">
-        <v>20.4287</v>
+        <v>-0.5723999999999998</v>
       </c>
       <c r="J3" t="n">
-        <v>32.7345</v>
+        <v>38.8268</v>
       </c>
       <c r="K3" t="n">
-        <v>7.0813</v>
+        <v>31.0758</v>
       </c>
       <c r="L3" t="n">
-        <v>25.6532</v>
+        <v>7.7508</v>
       </c>
       <c r="M3" t="n">
-        <v>-24.0822</v>
+        <v>-26.4371</v>
       </c>
       <c r="N3" t="n">
-        <v>-18.8573</v>
+        <v>-18.114</v>
       </c>
       <c r="O3" t="n">
-        <v>-5.2248</v>
+        <v>-8.323</v>
       </c>
       <c r="P3" t="n">
-        <v>20.812</v>
+        <v>-0.6244000000000005</v>
       </c>
       <c r="Q3" t="n">
-        <v>-23.5175</v>
+        <v>-46.2025</v>
       </c>
       <c r="R3" t="n">
-        <v>44.3292</v>
+        <v>45.5779</v>
       </c>
       <c r="S3" t="n">
-        <v>-9.4399</v>
+        <v>20.5458</v>
       </c>
       <c r="T3" t="n">
-        <v>-4.686599999999999</v>
+        <v>13.0069</v>
       </c>
       <c r="U3" t="n">
-        <v>-4.753</v>
+        <v>7.539099999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>18.0367</v>
+        <v>8.6752</v>
       </c>
       <c r="W3" t="n">
-        <v>25.8979</v>
+        <v>26.0749</v>
       </c>
       <c r="X3" t="n">
-        <v>-7.8613</v>
+        <v>-17.3996</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>36.3805</v>
+        <v>29.6756</v>
       </c>
       <c r="E4" t="n">
-        <v>28.1427</v>
+        <v>22.5987</v>
       </c>
       <c r="F4" t="n">
-        <v>8.2378</v>
+        <v>7.077100000000001</v>
       </c>
       <c r="G4" t="n">
         <v>-4.389200000000001</v>
@@ -766,13 +766,13 @@
         <v>22.4767</v>
       </c>
       <c r="S4" t="n">
-        <v>17.1439</v>
+        <v>10.4391</v>
       </c>
       <c r="T4" t="n">
-        <v>14.0323</v>
+        <v>8.488199999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1116</v>
+        <v>1.9506</v>
       </c>
       <c r="V4" t="n">
         <v>11.555</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>G. CLARKE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>34.137</v>
+        <v>27.5884</v>
       </c>
       <c r="E5" t="n">
-        <v>19.7967</v>
+        <v>32.3061</v>
       </c>
       <c r="F5" t="n">
-        <v>14.3405</v>
+        <v>-4.717599999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>17.7366</v>
+        <v>12.2833</v>
       </c>
       <c r="H5" t="n">
-        <v>11.6116</v>
+        <v>1.799799999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>6.1252</v>
+        <v>10.4835</v>
       </c>
       <c r="J5" t="n">
-        <v>27.791</v>
+        <v>42.07250000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>21.1682</v>
+        <v>23.0859</v>
       </c>
       <c r="L5" t="n">
-        <v>6.6232</v>
+        <v>18.9863</v>
       </c>
       <c r="M5" t="n">
-        <v>-10.0543</v>
+        <v>-29.7888</v>
       </c>
       <c r="N5" t="n">
-        <v>-9.5564</v>
+        <v>-21.286</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4976999999999999</v>
+        <v>-8.502699999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>3.9543</v>
+        <v>6.867500000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-29.1367</v>
+        <v>-31.2179</v>
       </c>
       <c r="R5" t="n">
-        <v>33.0908</v>
+        <v>38.0855</v>
       </c>
       <c r="S5" t="n">
-        <v>18.5174</v>
+        <v>2.5571</v>
       </c>
       <c r="T5" t="n">
-        <v>12.4566</v>
+        <v>2.2227</v>
       </c>
       <c r="U5" t="n">
-        <v>6.0606</v>
+        <v>0.3345</v>
       </c>
       <c r="V5" t="n">
-        <v>-6.071099999999999</v>
+        <v>5.8802</v>
       </c>
       <c r="W5" t="n">
-        <v>8.6858</v>
+        <v>19.2289</v>
       </c>
       <c r="X5" t="n">
-        <v>-14.7569</v>
+        <v>-13.3487</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>29.5451</v>
+        <v>25.2921</v>
       </c>
       <c r="E6" t="n">
-        <v>32.3091</v>
+        <v>12.5801</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.764</v>
+        <v>12.712</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.699399999999999</v>
+        <v>17.7366</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.851800000000001</v>
+        <v>11.6116</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1522</v>
+        <v>6.1252</v>
       </c>
       <c r="J6" t="n">
-        <v>12.4944</v>
+        <v>27.791</v>
       </c>
       <c r="K6" t="n">
-        <v>5.418999999999999</v>
+        <v>21.1682</v>
       </c>
       <c r="L6" t="n">
-        <v>7.075600000000001</v>
+        <v>6.6232</v>
       </c>
       <c r="M6" t="n">
-        <v>-18.194</v>
+        <v>-10.0543</v>
       </c>
       <c r="N6" t="n">
-        <v>-12.2708</v>
+        <v>-9.5564</v>
       </c>
       <c r="O6" t="n">
-        <v>-5.9229</v>
+        <v>-0.4976999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>11.2383</v>
+        <v>3.9543</v>
       </c>
       <c r="Q6" t="n">
-        <v>-16.8576</v>
+        <v>-29.1367</v>
       </c>
       <c r="R6" t="n">
-        <v>28.096</v>
+        <v>33.0908</v>
       </c>
       <c r="S6" t="n">
-        <v>41.0733</v>
+        <v>9.6722</v>
       </c>
       <c r="T6" t="n">
-        <v>31.2416</v>
+        <v>5.2401</v>
       </c>
       <c r="U6" t="n">
-        <v>9.8317</v>
+        <v>4.4321</v>
       </c>
       <c r="V6" t="n">
-        <v>-17.0674</v>
+        <v>-6.071099999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>5.431</v>
+        <v>8.6858</v>
       </c>
       <c r="X6" t="n">
-        <v>-22.4982</v>
+        <v>-14.7569</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>17.3292</v>
+        <v>24.6265</v>
       </c>
       <c r="E7" t="n">
-        <v>11.7879</v>
+        <v>17.3646</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5414</v>
+        <v>7.262</v>
       </c>
       <c r="G7" t="n">
         <v>19.0884</v>
@@ -1000,13 +1000,13 @@
         <v>20.8117</v>
       </c>
       <c r="S7" t="n">
-        <v>-4.6242</v>
+        <v>2.6732</v>
       </c>
       <c r="T7" t="n">
-        <v>-4.3573</v>
+        <v>1.2197</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2670999999999998</v>
+        <v>1.4534</v>
       </c>
       <c r="V7" t="n">
         <v>1.408199999999999</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>J. FRANCH DE PABLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>15.1132</v>
+        <v>16.9202</v>
       </c>
       <c r="E8" t="n">
-        <v>8.4618</v>
+        <v>10.0865</v>
       </c>
       <c r="F8" t="n">
-        <v>6.6515</v>
+        <v>6.8337</v>
       </c>
       <c r="G8" t="n">
-        <v>7.9962</v>
+        <v>9.0258</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.4198</v>
+        <v>-2.6557</v>
       </c>
       <c r="I8" t="n">
-        <v>11.4161</v>
+        <v>11.6811</v>
       </c>
       <c r="J8" t="n">
-        <v>26.7127</v>
+        <v>26.2521</v>
       </c>
       <c r="K8" t="n">
-        <v>9.6554</v>
+        <v>9.615200000000002</v>
       </c>
       <c r="L8" t="n">
-        <v>17.0573</v>
+        <v>16.6366</v>
       </c>
       <c r="M8" t="n">
-        <v>-18.7165</v>
+        <v>-17.2265</v>
       </c>
       <c r="N8" t="n">
-        <v>-13.0749</v>
+        <v>-12.2712</v>
       </c>
       <c r="O8" t="n">
-        <v>-5.6412</v>
+        <v>-4.955500000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>3.121700000000001</v>
+        <v>-1.6651</v>
       </c>
       <c r="Q8" t="n">
-        <v>-30.1773</v>
+        <v>-29.3448</v>
       </c>
       <c r="R8" t="n">
-        <v>33.2987</v>
+        <v>27.6797</v>
       </c>
       <c r="S8" t="n">
-        <v>10.4056</v>
+        <v>2.285600000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>8.565100000000001</v>
+        <v>0.2300000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8406</v>
+        <v>2.0554</v>
       </c>
       <c r="V8" t="n">
-        <v>-6.4108</v>
+        <v>7.274</v>
       </c>
       <c r="W8" t="n">
-        <v>3.3611</v>
+        <v>12.9489</v>
       </c>
       <c r="X8" t="n">
-        <v>-9.7719</v>
+        <v>-5.675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. CLARKE</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>13.3931</v>
+        <v>15.986</v>
       </c>
       <c r="E9" t="n">
-        <v>22.266</v>
+        <v>8.755899999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.872499999999999</v>
+        <v>7.230500000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>12.2833</v>
+        <v>7.9962</v>
       </c>
       <c r="H9" t="n">
-        <v>1.799799999999999</v>
+        <v>-3.4198</v>
       </c>
       <c r="I9" t="n">
-        <v>10.4835</v>
+        <v>11.4161</v>
       </c>
       <c r="J9" t="n">
-        <v>42.07250000000001</v>
+        <v>26.7127</v>
       </c>
       <c r="K9" t="n">
-        <v>23.0859</v>
+        <v>9.6554</v>
       </c>
       <c r="L9" t="n">
-        <v>18.9863</v>
+        <v>17.0573</v>
       </c>
       <c r="M9" t="n">
-        <v>-29.7888</v>
+        <v>-18.7165</v>
       </c>
       <c r="N9" t="n">
-        <v>-21.286</v>
+        <v>-13.0749</v>
       </c>
       <c r="O9" t="n">
-        <v>-8.502699999999999</v>
+        <v>-5.6412</v>
       </c>
       <c r="P9" t="n">
-        <v>6.867500000000001</v>
+        <v>3.121700000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-31.2179</v>
+        <v>-30.1773</v>
       </c>
       <c r="R9" t="n">
-        <v>38.0855</v>
+        <v>33.2987</v>
       </c>
       <c r="S9" t="n">
-        <v>-11.6385</v>
+        <v>11.279</v>
       </c>
       <c r="T9" t="n">
-        <v>-7.817</v>
+        <v>8.859</v>
       </c>
       <c r="U9" t="n">
-        <v>-3.8208</v>
+        <v>2.42</v>
       </c>
       <c r="V9" t="n">
-        <v>5.8802</v>
+        <v>-6.4108</v>
       </c>
       <c r="W9" t="n">
-        <v>19.2289</v>
+        <v>3.3611</v>
       </c>
       <c r="X9" t="n">
-        <v>-13.3487</v>
+        <v>-9.7719</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. FRANCH DE PABLO</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>9.555</v>
+        <v>10.1272</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2889</v>
+        <v>11.2945</v>
       </c>
       <c r="F10" t="n">
-        <v>6.2662</v>
+        <v>-1.1673</v>
       </c>
       <c r="G10" t="n">
-        <v>9.0258</v>
+        <v>-6.0404</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.6557</v>
+        <v>3.5347</v>
       </c>
       <c r="I10" t="n">
-        <v>11.6811</v>
+        <v>-9.575099999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>26.2521</v>
+        <v>18.7601</v>
       </c>
       <c r="K10" t="n">
-        <v>9.615200000000002</v>
+        <v>17.065</v>
       </c>
       <c r="L10" t="n">
-        <v>16.6366</v>
+        <v>1.695300000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-17.2265</v>
+        <v>-24.8006</v>
       </c>
       <c r="N10" t="n">
-        <v>-12.2712</v>
+        <v>-13.53</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.955500000000001</v>
+        <v>-11.2701</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6651</v>
+        <v>13.7359</v>
       </c>
       <c r="Q10" t="n">
-        <v>-29.3448</v>
+        <v>-28.5123</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6797</v>
+        <v>42.248</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.079400000000001</v>
+        <v>7.1231</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.5672</v>
+        <v>2.879</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4878</v>
+        <v>4.2439</v>
       </c>
       <c r="V10" t="n">
-        <v>7.274</v>
+        <v>-4.6914</v>
       </c>
       <c r="W10" t="n">
-        <v>12.9489</v>
+        <v>18.1674</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.675</v>
+        <v>-22.8587</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MOODY</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6799999999999997</v>
+        <v>7.473499999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8139</v>
+        <v>15.7143</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1339</v>
+        <v>-8.2408</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6418</v>
+        <v>-5.699399999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8399</v>
+        <v>-6.851800000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8018000000000001</v>
+        <v>1.1522</v>
       </c>
       <c r="J11" t="n">
-        <v>2.6456</v>
+        <v>12.4944</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4636</v>
+        <v>5.418999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1819999999999999</v>
+        <v>7.075600000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.2873</v>
+        <v>-18.194</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.3037</v>
+        <v>-12.2708</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9836999999999999</v>
+        <v>-5.9229</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8731</v>
+        <v>11.2383</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.3299</v>
+        <v>-16.8576</v>
       </c>
       <c r="R11" t="n">
-        <v>5.203</v>
+        <v>28.096</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9571000000000001</v>
+        <v>19.0022</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1719</v>
+        <v>14.6467</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2147</v>
+        <v>4.3551</v>
       </c>
       <c r="V11" t="n">
-        <v>2.4058</v>
+        <v>-17.0674</v>
       </c>
       <c r="W11" t="n">
-        <v>4.6702</v>
+        <v>5.431</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.2642</v>
+        <v>-22.4982</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. RAKOCEVIC</t>
+          <t>A. MOODY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3101</v>
+        <v>3.4424</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5787</v>
+        <v>4.766</v>
       </c>
       <c r="F12" t="n">
-        <v>2.888799999999999</v>
+        <v>-1.3236</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7003999999999999</v>
+        <v>-2.6418</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.4817</v>
+        <v>-1.8399</v>
       </c>
       <c r="I12" t="n">
-        <v>2.7814</v>
+        <v>-0.8018000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>2.4353</v>
+        <v>2.6456</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2973</v>
+        <v>2.4636</v>
       </c>
       <c r="L12" t="n">
-        <v>3.732699999999999</v>
+        <v>0.1819999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.1356</v>
+        <v>-5.2873</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.1846</v>
+        <v>-4.3037</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9512</v>
+        <v>-0.9836999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9137</v>
+        <v>1.8731</v>
       </c>
       <c r="Q12" t="n">
         <v>-3.3299</v>
       </c>
       <c r="R12" t="n">
-        <v>6.2435</v>
+        <v>5.203</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3631</v>
+        <v>1.8054</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.1439</v>
+        <v>0.7803</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2191</v>
+        <v>1.0251</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4599</v>
+        <v>2.4058</v>
       </c>
       <c r="W12" t="n">
-        <v>0.4599</v>
+        <v>4.6702</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.2642</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. VICENTE FERNANDEZ</t>
+          <t>N. RAKOCEVIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,67 +1420,67 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0509</v>
+        <v>2.7297</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5839</v>
+        <v>-0.7755000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.533</v>
+        <v>3.5052</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0404</v>
+        <v>-0.7003999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6119</v>
+        <v>-3.4817</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5715</v>
+        <v>2.7814</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3882</v>
+        <v>2.4353</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3262</v>
+        <v>-1.2973</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7144</v>
+        <v>3.732699999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4286</v>
+        <v>-3.1356</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2857</v>
+        <v>-2.1846</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1429</v>
+        <v>-0.9512</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2081</v>
+        <v>2.9137</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-3.3299</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2081</v>
+        <v>6.2435</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2995</v>
+        <v>0.05649999999999994</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1957</v>
+        <v>-0.3408</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1037</v>
+        <v>0.3975</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. ROMERO NARANJO</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1723</v>
+        <v>1.8863</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-8.672800000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1723</v>
+        <v>10.559</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.049</v>
+        <v>-6.012799999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1919</v>
+        <v>-3.2665</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1429</v>
+        <v>-2.7465</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-7.9389</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-4.3555</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-3.5834</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.049</v>
+        <v>1.9259</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1919</v>
+        <v>1.0892</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1429</v>
+        <v>0.8369000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.9541</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-6.451699999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>10.4058</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1233</v>
+        <v>3.4673</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.215</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1233</v>
+        <v>1.2522</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.4774999999999998</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.5026</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-3.025</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>A. VICENTE FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6878000000000001</v>
+        <v>0.115</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.8539</v>
+        <v>-0.4767</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1661</v>
+        <v>0.5917</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8871</v>
+        <v>0.0404</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3157</v>
+        <v>0.6119</v>
       </c>
       <c r="I15" t="n">
+        <v>-0.5715</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.3882</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.7144</v>
+      </c>
+      <c r="M15" t="n">
         <v>0.4286</v>
       </c>
-      <c r="J15" t="n">
-        <v>-1.4095</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-1.4095</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.2081</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="M15" t="n">
-        <v>0.5224</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.0939</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.4286</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-0.6244</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-1.0406</v>
-      </c>
       <c r="R15" t="n">
-        <v>0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0536</v>
+        <v>-0.1336</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5962999999999999</v>
+        <v>-0.0886</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4573</v>
+        <v>-0.045</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>R. ROMERO NARANJO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.742900000000001</v>
+        <v>-0.1429</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.9044</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>9.1616</v>
+        <v>-0.1429</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.012799999999999</v>
+        <v>-0.049</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.2665</v>
+        <v>-0.1919</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.7465</v>
+        <v>0.1429</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.9389</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.3555</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.5834</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9259</v>
+        <v>-0.049</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0892</v>
+        <v>-0.1919</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8369000000000001</v>
+        <v>0.1429</v>
       </c>
       <c r="P16" t="n">
-        <v>3.9541</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-6.451699999999999</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>10.4058</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1618999999999999</v>
+        <v>-0.0939</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.01650000000000007</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1454</v>
+        <v>-0.0939</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4774999999999998</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.5026</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. BERTAIN</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.4382</v>
+        <v>-1.2273</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.613</v>
+        <v>-2.2173</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8251999999999998</v>
+        <v>0.99</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.3096</v>
+        <v>-0.8871</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7224999999999999</v>
+        <v>-1.3157</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.5873</v>
+        <v>0.4286</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7048999999999999</v>
+        <v>-1.4095</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2089</v>
+        <v>-1.4095</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9138</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6048</v>
+        <v>0.5224</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9313</v>
+        <v>0.0939</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6735</v>
+        <v>0.4286</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6244</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2893</v>
+        <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9137</v>
+        <v>0.4162</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6904</v>
+        <v>0.5141</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3701</v>
+        <v>0.2329</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3203</v>
+        <v>0.2812</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9376</v>
+        <v>-0.23</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8137</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>N. BERTAIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.6943</v>
+        <v>-2.2107</v>
       </c>
       <c r="E18" t="n">
-        <v>2.237399999999999</v>
+        <v>-1.411</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.9315</v>
+        <v>-0.7998000000000002</v>
       </c>
       <c r="G18" t="n">
-        <v>-6.0404</v>
+        <v>-3.3096</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5347</v>
+        <v>-0.7224999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-9.575099999999999</v>
+        <v>-2.5873</v>
       </c>
       <c r="J18" t="n">
-        <v>18.7601</v>
+        <v>-0.7048999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>17.065</v>
+        <v>1.2089</v>
       </c>
       <c r="L18" t="n">
-        <v>1.695300000000001</v>
+        <v>-1.9138</v>
       </c>
       <c r="M18" t="n">
-        <v>-24.8006</v>
+        <v>-2.6048</v>
       </c>
       <c r="N18" t="n">
-        <v>-13.53</v>
+        <v>-1.9313</v>
       </c>
       <c r="O18" t="n">
-        <v>-11.2701</v>
+        <v>-0.6735</v>
       </c>
       <c r="P18" t="n">
-        <v>13.7359</v>
+        <v>0.6244</v>
       </c>
       <c r="Q18" t="n">
-        <v>-28.5123</v>
+        <v>-2.2893</v>
       </c>
       <c r="R18" t="n">
-        <v>42.248</v>
+        <v>2.9137</v>
       </c>
       <c r="S18" t="n">
-        <v>-6.698399999999999</v>
+        <v>-0.4629</v>
       </c>
       <c r="T18" t="n">
-        <v>-6.1783</v>
+        <v>-0.168</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5202000000000002</v>
+        <v>-0.2949</v>
       </c>
       <c r="V18" t="n">
-        <v>-4.6914</v>
+        <v>0.9376</v>
       </c>
       <c r="W18" t="n">
-        <v>18.1674</v>
+        <v>1.7513</v>
       </c>
       <c r="X18" t="n">
-        <v>-22.8587</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. OKAFOR</t>
+          <t>M. BILALOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>-15.1327</v>
+        <v>-14.4483</v>
       </c>
       <c r="E19" t="n">
-        <v>-17.2886</v>
+        <v>-17.3923</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1558</v>
+        <v>2.9441</v>
       </c>
       <c r="G19" t="n">
-        <v>-13.5858</v>
+        <v>-18.8914</v>
       </c>
       <c r="H19" t="n">
-        <v>-10.8583</v>
+        <v>-20.3625</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.7278</v>
+        <v>1.4712</v>
       </c>
       <c r="J19" t="n">
-        <v>-10.8297</v>
+        <v>-6.8048</v>
       </c>
       <c r="K19" t="n">
-        <v>-8.9428</v>
+        <v>-9.0473</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.8867</v>
+        <v>2.2424</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7564</v>
+        <v>-12.0865</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9155</v>
+        <v>-11.315</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8408000000000001</v>
+        <v>-0.7717000000000002</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.665</v>
+        <v>2.9137</v>
       </c>
       <c r="Q19" t="n">
-        <v>-7.4923</v>
+        <v>-20.3957</v>
       </c>
       <c r="R19" t="n">
-        <v>5.827299999999999</v>
+        <v>23.3092</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1181000000000001</v>
+        <v>4.6215</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8242</v>
+        <v>4.1122</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9424</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-3.0922</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8575</v>
+        <v>5.6961</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8575</v>
+        <v>-8.7883</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. BILALOVIC</t>
+          <t>O. OKAFOR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>-20.7042</v>
+        <v>-14.5224</v>
       </c>
       <c r="E20" t="n">
-        <v>-21.9022</v>
+        <v>-16.8133</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1981</v>
+        <v>2.2909</v>
       </c>
       <c r="G20" t="n">
-        <v>-18.8914</v>
+        <v>-13.5858</v>
       </c>
       <c r="H20" t="n">
-        <v>-20.3625</v>
+        <v>-10.8583</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4712</v>
+        <v>-2.7278</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.8048</v>
+        <v>-10.8297</v>
       </c>
       <c r="K20" t="n">
-        <v>-9.0473</v>
+        <v>-8.9428</v>
       </c>
       <c r="L20" t="n">
-        <v>2.2424</v>
+        <v>-1.8867</v>
       </c>
       <c r="M20" t="n">
-        <v>-12.0865</v>
+        <v>-2.7564</v>
       </c>
       <c r="N20" t="n">
-        <v>-11.315</v>
+        <v>-1.9155</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7717000000000002</v>
+        <v>-0.8408000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9137</v>
+        <v>-1.665</v>
       </c>
       <c r="Q20" t="n">
-        <v>-20.3957</v>
+        <v>-7.4923</v>
       </c>
       <c r="R20" t="n">
-        <v>23.3092</v>
+        <v>5.827299999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6342</v>
+        <v>0.7284999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3979</v>
+        <v>-0.3489</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2364</v>
+        <v>1.0772</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.0922</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="W20" t="n">
-        <v>5.6961</v>
+        <v>1.8575</v>
       </c>
       <c r="X20" t="n">
-        <v>-8.7883</v>
+        <v>-1.8575</v>
       </c>
     </row>
     <row r="21">
@@ -2047,19 +2047,19 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>202.8259</v>
+        <v>223.8268</v>
       </c>
       <c r="E21" t="n">
-        <v>147.7995</v>
+        <v>156.6072</v>
       </c>
       <c r="F21" t="n">
-        <v>55.027</v>
+        <v>67.2205</v>
       </c>
       <c r="G21" t="n">
         <v>25.0059</v>
       </c>
       <c r="H21" t="n">
-        <v>-28.5719</v>
+        <v>-28.57190000000001</v>
       </c>
       <c r="I21" t="n">
         <v>53.5776</v>
@@ -2083,7 +2083,7 @@
         <v>-53.5132</v>
       </c>
       <c r="P21" t="n">
-        <v>81.16560000000001</v>
+        <v>81.16559999999998</v>
       </c>
       <c r="Q21" t="n">
         <v>-309.057</v>
@@ -2092,13 +2092,13 @@
         <v>390.2209999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>77.10690000000002</v>
+        <v>98.10859999999998</v>
       </c>
       <c r="T21" t="n">
-        <v>56.4575</v>
+        <v>65.26489999999998</v>
       </c>
       <c r="U21" t="n">
-        <v>20.65</v>
+        <v>32.8432</v>
       </c>
       <c r="V21" t="n">
         <v>19.5472</v>
